--- a/data/homes5.xlsx
+++ b/data/homes5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ATS\crm_bunyodkorhouse\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{46421390-EEB9-4E4D-96D8-EDE91B78D673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A45F832-BFED-4B98-B4D7-D9A6C62A0855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{2801F4C1-7D31-4E77-9C3E-1A1FD9E180E7}"/>
   </bookViews>
@@ -533,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3B8FA16-A4BF-4211-A236-8FD53C7898D2}">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21.6640625" customWidth="1"/>
@@ -1171,6 +1171,74 @@
         <v>7000000</v>
       </c>
     </row>
+    <row r="38" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
+        <v>-1</v>
+      </c>
+      <c r="B38" s="3">
+        <v>234</v>
+      </c>
+      <c r="C38" s="3">
+        <v>59</v>
+      </c>
+      <c r="D38" s="3">
+        <v>2</v>
+      </c>
+      <c r="E38" s="3">
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="4">
+        <v>-1</v>
+      </c>
+      <c r="B39" s="5">
+        <v>235</v>
+      </c>
+      <c r="C39" s="5">
+        <v>62.5</v>
+      </c>
+      <c r="D39" s="5">
+        <v>2</v>
+      </c>
+      <c r="E39" s="5">
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="4">
+        <v>-1</v>
+      </c>
+      <c r="B40" s="5">
+        <v>236</v>
+      </c>
+      <c r="C40" s="5">
+        <v>64</v>
+      </c>
+      <c r="D40" s="5">
+        <v>2</v>
+      </c>
+      <c r="E40" s="5">
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="6">
+        <v>-1</v>
+      </c>
+      <c r="B41" s="7">
+        <v>237</v>
+      </c>
+      <c r="C41" s="7">
+        <v>59</v>
+      </c>
+      <c r="D41" s="7">
+        <v>2</v>
+      </c>
+      <c r="E41" s="7">
+        <v>7000000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
